--- a/baikal_rashod.xlsx
+++ b/baikal_rashod.xlsx
@@ -70,9 +70,6 @@
     <t>шт</t>
   </si>
   <si>
-    <t>Индивидуальный предприниматель Батршин Р.Р</t>
-  </si>
-  <si>
     <r>
       <t>приход</t>
     </r>
@@ -85,6 +82,9 @@
       </rPr>
       <t>/расход</t>
     </r>
+  </si>
+  <si>
+    <t>Индивидуальный предприниматель Саляхова Э.Н.</t>
   </si>
 </sst>
 </file>
@@ -680,7 +680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -712,7 +712,7 @@
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F1" s="5"/>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -739,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9">
-        <v>742005782889</v>
+        <v>745083339895</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
